--- a/ci-cd-merge-resolver/repoCollector/datasets/openapi-generator.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/openapi-generator.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="130">
   <si>
     <t>mergeCommit</t>
   </si>
@@ -44,160 +44,364 @@
     <t>isMultiModule</t>
   </si>
   <si>
-    <t>be214dc349641b754b91f4d1319437b1f3898081</t>
-  </si>
-  <si>
-    <t>1c1c6b465feaec5f8af463bda7c288cb033c244a</t>
-  </si>
-  <si>
-    <t>560bf7e080518f1c5e9af41acdbf3fa402d75512</t>
-  </si>
-  <si>
-    <t>95d356ab6b12360536411211e93b5ef2f2d62606</t>
-  </si>
-  <si>
-    <t>ad137ec84acde1ddd06e2572b67476725b926581</t>
-  </si>
-  <si>
-    <t>3a0eb9d040fb89185fbada972159805c4deb77bf</t>
-  </si>
-  <si>
-    <t>35f933b27faaa68f89a89efb2efb3e2db511ba6c</t>
-  </si>
-  <si>
-    <t>702e27465912674bf6ca5760d24e05b1be308efd</t>
-  </si>
-  <si>
-    <t>39fbf53150456c20af038f4511a72dc986a06855</t>
-  </si>
-  <si>
-    <t>6cae0fbb78ff4daad12e23969faf660a7cefa0bd</t>
-  </si>
-  <si>
-    <t>9e412edb640a8e7e49db1ecc24958fdc9a50533e</t>
-  </si>
-  <si>
-    <t>5bd94b8fa0515cd2ba0e601959bf8eea452aea3a</t>
-  </si>
-  <si>
-    <t>3594b3452ddf6640151b7cfc2177ee1a18f27977</t>
-  </si>
-  <si>
-    <t>afacdb229a872ec1443f334bc336edf91b192229</t>
-  </si>
-  <si>
-    <t>42f4e863b7e4e141ce2a77c0a7a50e4742c957fa</t>
-  </si>
-  <si>
-    <t>eb75515715c60e0de827d7e2162c61bdd1899195</t>
-  </si>
-  <si>
-    <t>bd61978b5f0a90e42d621807d0197eb6c3e7f1c1</t>
-  </si>
-  <si>
-    <t>f6001c2768191d3ae2d5984968e9d65461a184bf</t>
-  </si>
-  <si>
-    <t>3e81876e2cc363f55939f538c9d1c475a300ca8b</t>
-  </si>
-  <si>
-    <t>ca225e48271750ff626bceff686e5811f4d49bdd</t>
-  </si>
-  <si>
-    <t>c7fcb39a2d66c6748f07dc8d258625885facf649</t>
-  </si>
-  <si>
-    <t>0e1164ff6b72aae0542b9b836f2428cc10bf697a</t>
-  </si>
-  <si>
-    <t>4a36be70025e9c0d3ff61731618b7fc2d942c4b6</t>
-  </si>
-  <si>
-    <t>c8b84c4d0314aaff6e44c6c879b21e202af7ff30</t>
-  </si>
-  <si>
-    <t>764a462711c53920f7a6f7dfa403889783ebf58a</t>
-  </si>
-  <si>
-    <t>8403e59aa03d0099b7c6872b9b884a3d83d05b9a</t>
-  </si>
-  <si>
-    <t>3825a20ddc41914f79ffcc810b069c57717e58ee</t>
-  </si>
-  <si>
-    <t>12e03b193794e23afb643c48d6cc40cbeef2aed0</t>
-  </si>
-  <si>
-    <t>27e6d08be433a97bcf656496068554956dd91919</t>
-  </si>
-  <si>
-    <t>8d532d5a38b976611534cc66291ca0cda8d0d60c</t>
-  </si>
-  <si>
-    <t>9c3d4ef2a6406a7d7f1af390649e55ab05fcd047</t>
-  </si>
-  <si>
-    <t>3ed6343933a27b8069e52f0bdf795b278f37a066</t>
-  </si>
-  <si>
-    <t>8d16239aaba9c21873db2208ccc495e2714952da</t>
-  </si>
-  <si>
-    <t>82b77a099af27acdfbf41d47382a73226c266483</t>
-  </si>
-  <si>
-    <t>676da0e77831bb55d637324769976bff8e0da17a</t>
-  </si>
-  <si>
-    <t>6bfef6c191659e2233ed1b880af84241e262dc33</t>
-  </si>
-  <si>
-    <t>c54b0623b8ccfb19d910802854bc67ff7894acdf</t>
-  </si>
-  <si>
-    <t>b88666b87acab1d59f5a1502c2445bf390ae8dfe</t>
-  </si>
-  <si>
-    <t>2bac0a8d99789a9c98897bd5f688e4f35f85dd2f</t>
-  </si>
-  <si>
-    <t>6ba97321ff494ef6f7825505159f55cce251fb44</t>
-  </si>
-  <si>
-    <t>3bd2a611bf39146fc5395080509f470423b8f82c</t>
-  </si>
-  <si>
-    <t>2947d147b47e165c1bee23503e8ff8bd02515146</t>
-  </si>
-  <si>
-    <t>b0ce532bdc7436bf1ba377af5a72e5681565f2df</t>
-  </si>
-  <si>
-    <t>f8e15f1f96d5ac6de6ce6396651361f2c4525995</t>
-  </si>
-  <si>
-    <t>7f8b853f502d9039c9a0aac2614ce92871e895ed</t>
-  </si>
-  <si>
-    <t>1d2d56ab65ce65dc2b596d87218666da2ff76fde</t>
-  </si>
-  <si>
-    <t>935146d1872e48966bdef4ef5463aec39bb9f151</t>
-  </si>
-  <si>
-    <t>c0322b18a407d7aedc3830b560159f57a010c9b9</t>
-  </si>
-  <si>
-    <t>e852ceceefab32e9b70f6a5156c446a42d128415</t>
-  </si>
-  <si>
-    <t>1beec7ef87f14afe53d889916e3c04de319cd0c8</t>
-  </si>
-  <si>
-    <t>fb18e7a039aa000231a261bac17582d4c91884be</t>
-  </si>
-  <si>
-    <t>39e27a804d898519febb7ef349cda041e7daa77c</t>
+    <t>1fc969b050634833b9a237c16774f63db6b9785b</t>
+  </si>
+  <si>
+    <t>c5d1c5d73bfcde6aa83dcc1914e50645fff6cc71</t>
+  </si>
+  <si>
+    <t>7406d07acaa82cf48cdfb4696c727d8159764d50</t>
+  </si>
+  <si>
+    <t>fee54157c0b6c703d1e856b30dd2ac487d04c36a</t>
+  </si>
+  <si>
+    <t>29a0159add1fce330e1c350fe8dab7c3f7173b3e</t>
+  </si>
+  <si>
+    <t>85850b28468e022179bf33838302a2e4b0d2235b</t>
+  </si>
+  <si>
+    <t>98684d872cd18ccf70cb15266a91a1c2a928a7d0</t>
+  </si>
+  <si>
+    <t>b671129557d11766ab97f900c8dbed4542ccc2e8</t>
+  </si>
+  <si>
+    <t>77555bfab10a6a394af44ca341b4ae7ae24523a3</t>
+  </si>
+  <si>
+    <t>45ff39c237eebc62d35201d9e3eeee8a6716883e</t>
+  </si>
+  <si>
+    <t>cfd9d7e4c6875dc3103fa48402b022adac61e037</t>
+  </si>
+  <si>
+    <t>9b68f02f83cf653ea4d8c0758d439f1598fdb553</t>
+  </si>
+  <si>
+    <t>82740de5a027abcdce8bd980cd8be7fc701626cd</t>
+  </si>
+  <si>
+    <t>5c46929ec2e9c5bc947f2e59c236c61cb06e9396</t>
+  </si>
+  <si>
+    <t>1c8e07a944d70fe1fcf4646a003ec83a2cadb91b</t>
+  </si>
+  <si>
+    <t>0bb610494e6e91a7a67b3fa82049d55c85e05bc4</t>
+  </si>
+  <si>
+    <t>1f1e92d96409abe37a6b7f72bab25072f0244cd7</t>
+  </si>
+  <si>
+    <t>5dcda94164d97cb29b9c5753848eab28b01a509b</t>
+  </si>
+  <si>
+    <t>2ac169c750f2b4f3fbf5ecbea608cd0c82b8040d</t>
+  </si>
+  <si>
+    <t>b5949f61e4f66c86cb1082fa5320164f211245c4</t>
+  </si>
+  <si>
+    <t>2324e927bd2b058604eec1fea5d904773de036c4</t>
+  </si>
+  <si>
+    <t>7fc36f1e1ecedc33b5e67616313ce0dd743c94e4</t>
+  </si>
+  <si>
+    <t>fb04b5a26a31a079e985f8422177dce92f0b6a03</t>
+  </si>
+  <si>
+    <t>9c46ab2599924fc4f4d3720adfe085c4a5c66fa6</t>
+  </si>
+  <si>
+    <t>18e6440bcc766e2ee6ed5aa072085051fb94e8bf</t>
+  </si>
+  <si>
+    <t>009a039fc541897075ba0a646ed316c962092235</t>
+  </si>
+  <si>
+    <t>b84769d1e37d54ea5fe0c2220678f7f9ab9f05b8</t>
+  </si>
+  <si>
+    <t>0a67696de875d357318fa044bc549bcc8c1f9041</t>
+  </si>
+  <si>
+    <t>27686c7e6486e44805bbc2d18afaf113b2b0b3a7</t>
+  </si>
+  <si>
+    <t>7d22605473c4a779608286ae8bb1d4e8623b07ff</t>
+  </si>
+  <si>
+    <t>fb357086c8c368ebdf060aa292f18406566911a0</t>
+  </si>
+  <si>
+    <t>1700a86c3807cc0f80d0589e48f4be2dffdc4168</t>
+  </si>
+  <si>
+    <t>1e9fe51175dc0329f28624b42621b6464dd64b2f</t>
+  </si>
+  <si>
+    <t>12bcb18e9ed1821bff757ca771b62b214005ec3d</t>
+  </si>
+  <si>
+    <t>022eb0d379a057fd386e04deb16184f1b07302f8</t>
+  </si>
+  <si>
+    <t>b185d03a1b25247c40a9bd1d9a35dafa0453c894</t>
+  </si>
+  <si>
+    <t>e1e5ac4d379234ac8d4525deb8fa7be983cc1e8c</t>
+  </si>
+  <si>
+    <t>41cfcc6f236622c9769c3d5f768d3b7273389be7</t>
+  </si>
+  <si>
+    <t>a6b7f60ac74a4cc525d5e93e23bdfed7ae0d46d8</t>
+  </si>
+  <si>
+    <t>c988afa766ebadb180cdbacaaec8008c52c57d2f</t>
+  </si>
+  <si>
+    <t>e0ec4548911b79e3d069e0cdeb32a41223e17106</t>
+  </si>
+  <si>
+    <t>3a3285779064fd60f2fe2438eb2f86171cdc1a33</t>
+  </si>
+  <si>
+    <t>87bbbc1a1bb4d6e987e2e96ae964cb48fc278cea</t>
+  </si>
+  <si>
+    <t>d7202a7c76e77205d608084fbcfff7ab643e0677</t>
+  </si>
+  <si>
+    <t>6ee332a5130f471c264c266af29247a8004e9131</t>
+  </si>
+  <si>
+    <t>c05db535e1eb35c1431c245f275bd89d72b16457</t>
+  </si>
+  <si>
+    <t>5d14f3f733dd3af31acbb470e71bd684ea2b1462</t>
+  </si>
+  <si>
+    <t>09e2bbe1eec015bb8c4455e34c3ad15a98d90797</t>
+  </si>
+  <si>
+    <t>7b57dd0c04e215577a348f96e83326276b41aff6</t>
+  </si>
+  <si>
+    <t>3c9b495eb1e1183e4d1b8c8e18c89113636a94fe</t>
+  </si>
+  <si>
+    <t>42a5a13fef6677ff41920926eb37e4edcd6cbffa</t>
+  </si>
+  <si>
+    <t>413a00ef40337e469d5b8fcbbe01b22d13500857</t>
+  </si>
+  <si>
+    <t>1091ebce5a12062acde5e2c984d801682fcfd5a6</t>
+  </si>
+  <si>
+    <t>3744a3f8f57eb795b94072d4d80357142ea9663f</t>
+  </si>
+  <si>
+    <t>e964702550b12276915979cadfdb82a181f52f71</t>
+  </si>
+  <si>
+    <t>0876c9d408ddf6bc10e3ccb19030cf46d25f935f</t>
+  </si>
+  <si>
+    <t>0416b0332f36b4a7f80a4313df8f8257a4539fe4</t>
+  </si>
+  <si>
+    <t>9a56d4560ab5986afd68a842e6deaf6f7bded4b3</t>
+  </si>
+  <si>
+    <t>25a46374c59536cdf90c3bada10af962d728605d</t>
+  </si>
+  <si>
+    <t>ecf924e78f3c791cf35ff1e51799799e29d1d2ea</t>
+  </si>
+  <si>
+    <t>f4d78079ded2283a1080f70da8ad8865ae6b0e7f</t>
+  </si>
+  <si>
+    <t>5eefbc2195ac309e033f5dce719ab11d5b2e1faa</t>
+  </si>
+  <si>
+    <t>9269dac6cf70f6ac83ae8778e40d50a8c19d4453</t>
+  </si>
+  <si>
+    <t>40369bb81951e446e5fc8692d042284c3937145e</t>
+  </si>
+  <si>
+    <t>7fa53773fcf09eb80d7b5d0457908f2557f4bb82</t>
+  </si>
+  <si>
+    <t>aef25ffdc3bfa3d319c6136f9500a8c03a99e34a</t>
+  </si>
+  <si>
+    <t>702f193f6191a8f6d0b59f2d34292c616e7bcc4d</t>
+  </si>
+  <si>
+    <t>2dd051fd4e9099686576a687ea60f500885f4de0</t>
+  </si>
+  <si>
+    <t>5c4a05e21273c1518d903b3a0d778eb8821c939e</t>
+  </si>
+  <si>
+    <t>745951c1cef70e56fca248797aa2a57b5de38ce1</t>
+  </si>
+  <si>
+    <t>3ef7694b9f6803d8df84f5a76d1c7bc830b38fdb</t>
+  </si>
+  <si>
+    <t>59801d51672c7a33b6f5c2796992fdb428a02467</t>
+  </si>
+  <si>
+    <t>c14da15b3ef451a2ed50fdbec88656ed758dc982</t>
+  </si>
+  <si>
+    <t>f7cbb2c0e62fa169de8d0c7a75465eff57cdbe4c</t>
+  </si>
+  <si>
+    <t>3ed1aa8e79687bed63dfa064de27317273080471</t>
+  </si>
+  <si>
+    <t>6685f18e5f789915459c527a8749f034a0bcbba1</t>
+  </si>
+  <si>
+    <t>956e7b4cb5b94a36935aa633b31b46a9877d584d</t>
+  </si>
+  <si>
+    <t>ad2552ace61738a337c3f62088ae0d66f1ba7086</t>
+  </si>
+  <si>
+    <t>22c80588f63629a17ae0113da11e2d9b437bd4cf</t>
+  </si>
+  <si>
+    <t>e969b35ea2416fb187ce40ddb80ab1b0202eff49</t>
+  </si>
+  <si>
+    <t>863f431dfbd8585d0942e38c7e29b7f071c57a70</t>
+  </si>
+  <si>
+    <t>dc89f3e731d1756c95e9360977c3f9db4d97465d</t>
+  </si>
+  <si>
+    <t>e41dd761b5e2f0e9d515baa5ddbf5e77f482ae6e</t>
+  </si>
+  <si>
+    <t>f4d1261522577c6eaeff723163d1daaa10900fe3</t>
+  </si>
+  <si>
+    <t>ab9f5fa0c06ef37621332afe4c4f5efd105bc44d</t>
+  </si>
+  <si>
+    <t>640b16b58a4c9131c18e53f03c204ac1b7fee3c5</t>
+  </si>
+  <si>
+    <t>8153284f071ddb368597e23f7953906999c9fbf0</t>
+  </si>
+  <si>
+    <t>e66566a9710a5f65e89986bac8fe533164e5a3a6</t>
+  </si>
+  <si>
+    <t>50c6f87d986caa3915ba3666dea5cba8c036bcb8</t>
+  </si>
+  <si>
+    <t>942c77b53086ab88b42d40e4cecb9a72ccbacfb8</t>
+  </si>
+  <si>
+    <t>0682e41d6deefddfc5b35078a903b2cac6d482fc</t>
+  </si>
+  <si>
+    <t>8f37e6804980ab2bacf253e232d1a63f8f433f92</t>
+  </si>
+  <si>
+    <t>39fb77ad3e2e71acd9850438659bfd74e2a6d79e</t>
+  </si>
+  <si>
+    <t>b91ff65204ac09663da1fa9ee75ebee39e5b8d7f</t>
+  </si>
+  <si>
+    <t>05a3c8d5dfc894d74592260534846320f96ba2d0</t>
+  </si>
+  <si>
+    <t>b275b8f9dab0b9e153cdf24e2ae9a16935bf8211</t>
+  </si>
+  <si>
+    <t>ad4de91d92875b753c80848bf1f6350ffc7e1646</t>
+  </si>
+  <si>
+    <t>bed3cfcfdcf5c43246ee5af4584e601064662f6e</t>
+  </si>
+  <si>
+    <t>db71d97370f4af37ddff81925e39e3cb080efa7d</t>
+  </si>
+  <si>
+    <t>1f4261d20b2ac43f00b3f395565c738c74a64b4e</t>
+  </si>
+  <si>
+    <t>0e65f649bc59ea668d6965b4f44f7b02175c6d62</t>
+  </si>
+  <si>
+    <t>1fdd3e6ffa7e8b43c65327fd7b5619e84aa24680</t>
+  </si>
+  <si>
+    <t>a774ff9587587c8dec51163ba5ff2d4494f5b1ec</t>
+  </si>
+  <si>
+    <t>4452fdbc0253be1f4597beaa0f094aeda23cb46e</t>
+  </si>
+  <si>
+    <t>78c4928908da47982153f1e3130e8b6041d73249</t>
+  </si>
+  <si>
+    <t>08d4545947451c849dcc7713d1155e6851d82445</t>
+  </si>
+  <si>
+    <t>f477ae83aab64a76adc3d22b555f64127300bef0</t>
+  </si>
+  <si>
+    <t>090d80b42c70735aed81b4ae47102273acb604f9</t>
+  </si>
+  <si>
+    <t>bea9e265e9da94996bd3b3f861ad53b7d7e789b1</t>
+  </si>
+  <si>
+    <t>439dbb11214e263fed62a5317f485083129caa5e</t>
+  </si>
+  <si>
+    <t>f064d29e828305c0f72c8d417d92cbbf8bcc7582</t>
+  </si>
+  <si>
+    <t>22fcea1c910bdf8c65c776926ace204cb210d10e</t>
+  </si>
+  <si>
+    <t>21da8b6d9cf3f063cd0d124ccd474dd49242779d</t>
+  </si>
+  <si>
+    <t>5c3fe23e9f558f3337676125eb5a17532315d397</t>
+  </si>
+  <si>
+    <t>20cc80d170c730bfefb805ae971a0f31fad70b06</t>
+  </si>
+  <si>
+    <t>9acefcffddc7af34623f4b515e5f8e19e2ffe9a3</t>
+  </si>
+  <si>
+    <t>9b113d5a192e8c9bd5d54cf7b173d93fc715f84b</t>
+  </si>
+  <si>
+    <t>e1b1edf95897b9c3973316e5ac88f8c6e598893e</t>
+  </si>
+  <si>
+    <t>9be178b26a3859f9522fc5d63201e67c47c47855</t>
+  </si>
+  <si>
+    <t>26b618241ad70467aa504d0eb7699e0baf84fb42</t>
   </si>
 </sst>
 </file>
@@ -242,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -288,13 +492,13 @@
         <v>12</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>15.0</v>
+        <v>646.0</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>652.0</v>
+        <v>97.0</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>125.0</v>
+        <v>95.0</v>
       </c>
       <c r="G2" t="b" s="0">
         <v>0</v>
@@ -303,10 +507,10 @@
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>1.9119999408721924</v>
+        <v>20.26799964904785</v>
       </c>
       <c r="J2" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -320,13 +524,13 @@
         <v>15</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>15.0</v>
+        <v>669.0</v>
       </c>
       <c r="E3" t="n" s="0">
-        <v>647.0</v>
+        <v>8.0</v>
       </c>
       <c r="F3" t="n" s="0">
-        <v>123.0</v>
+        <v>1.0</v>
       </c>
       <c r="G3" t="b" s="0">
         <v>0</v>
@@ -335,10 +539,10 @@
         <v>1</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>1.4919999837875366</v>
+        <v>27.972999572753906</v>
       </c>
       <c r="J3" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -352,13 +556,13 @@
         <v>18</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>15.0</v>
+        <v>663.0</v>
       </c>
       <c r="E4" t="n" s="0">
-        <v>654.0</v>
+        <v>32.0</v>
       </c>
       <c r="F4" t="n" s="0">
-        <v>125.0</v>
+        <v>24.0</v>
       </c>
       <c r="G4" t="b" s="0">
         <v>0</v>
@@ -367,10 +571,10 @@
         <v>1</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>1.7389999628067017</v>
+        <v>24.02199935913086</v>
       </c>
       <c r="J4" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -384,13 +588,13 @@
         <v>21</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>15.0</v>
+        <v>647.0</v>
       </c>
       <c r="E5" t="n" s="0">
-        <v>797.0</v>
+        <v>53.0</v>
       </c>
       <c r="F5" t="n" s="0">
-        <v>175.0</v>
+        <v>19.0</v>
       </c>
       <c r="G5" t="b" s="0">
         <v>0</v>
@@ -399,10 +603,10 @@
         <v>1</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>1.1759999990463257</v>
+        <v>18.386999130249023</v>
       </c>
       <c r="J5" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -416,13 +620,13 @@
         <v>24</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>1544.0</v>
+        <v>651.0</v>
       </c>
       <c r="E6" t="n" s="0">
-        <v>686.0</v>
+        <v>1.0</v>
       </c>
       <c r="F6" t="n" s="0">
-        <v>122.0</v>
+        <v>1.0</v>
       </c>
       <c r="G6" t="b" s="0">
         <v>0</v>
@@ -431,10 +635,10 @@
         <v>1</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>247.322021484375</v>
+        <v>20.56399917602539</v>
       </c>
       <c r="J6" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -448,13 +652,13 @@
         <v>27</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>15.0</v>
+        <v>666.0</v>
       </c>
       <c r="E7" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F7" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G7" t="b" s="0">
         <v>0</v>
@@ -463,10 +667,10 @@
         <v>1</v>
       </c>
       <c r="I7" t="n" s="0">
-        <v>3.1440000534057617</v>
+        <v>25.20800018310547</v>
       </c>
       <c r="J7" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -480,13 +684,13 @@
         <v>30</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>15.0</v>
+        <v>649.0</v>
       </c>
       <c r="E8" t="n" s="0">
-        <v>637.0</v>
+        <v>3.0</v>
       </c>
       <c r="F8" t="n" s="0">
-        <v>123.0</v>
+        <v>3.0</v>
       </c>
       <c r="G8" t="b" s="0">
         <v>0</v>
@@ -495,10 +699,10 @@
         <v>1</v>
       </c>
       <c r="I8" t="n" s="0">
-        <v>1.9149999618530273</v>
+        <v>18.61400032043457</v>
       </c>
       <c r="J8" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -512,13 +716,13 @@
         <v>33</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>15.0</v>
+        <v>649.0</v>
       </c>
       <c r="E9" t="n" s="0">
-        <v>788.0</v>
+        <v>4.0</v>
       </c>
       <c r="F9" t="n" s="0">
-        <v>189.0</v>
+        <v>2.0</v>
       </c>
       <c r="G9" t="b" s="0">
         <v>0</v>
@@ -527,10 +731,10 @@
         <v>1</v>
       </c>
       <c r="I9" t="n" s="0">
-        <v>1.4700000286102295</v>
+        <v>22.01799964904785</v>
       </c>
       <c r="J9" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -544,13 +748,13 @@
         <v>36</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>15.0</v>
+        <v>654.0</v>
       </c>
       <c r="E10" t="n" s="0">
-        <v>673.0</v>
+        <v>6.0</v>
       </c>
       <c r="F10" t="n" s="0">
-        <v>125.0</v>
+        <v>2.0</v>
       </c>
       <c r="G10" t="b" s="0">
         <v>0</v>
@@ -559,10 +763,10 @@
         <v>1</v>
       </c>
       <c r="I10" t="n" s="0">
-        <v>3.927000045776367</v>
+        <v>22.90999984741211</v>
       </c>
       <c r="J10" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -576,14 +780,14 @@
         <v>39</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>15.0</v>
+        <v>646.0</v>
       </c>
       <c r="E11" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="F11" t="n" s="0">
         <v>9.0</v>
       </c>
-      <c r="F11" t="n" s="0">
-        <v>3.0</v>
-      </c>
       <c r="G11" t="b" s="0">
         <v>0</v>
       </c>
@@ -591,27 +795,27 @@
         <v>1</v>
       </c>
       <c r="I11" t="n" s="0">
-        <v>1.284000039100647</v>
+        <v>20.305999755859375</v>
       </c>
       <c r="J11" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>15.0</v>
+        <v>646.0</v>
       </c>
       <c r="E12" t="n" s="0">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="F12" t="n" s="0">
         <v>5.0</v>
@@ -623,30 +827,30 @@
         <v>1</v>
       </c>
       <c r="I12" t="n" s="0">
-        <v>1.5080000162124634</v>
+        <v>24.18600082397461</v>
       </c>
       <c r="J12" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>63.0</v>
+        <v>666.0</v>
       </c>
       <c r="E13" t="n" s="0">
-        <v>690.0</v>
+        <v>30.0</v>
       </c>
       <c r="F13" t="n" s="0">
-        <v>122.0</v>
+        <v>28.0</v>
       </c>
       <c r="G13" t="b" s="0">
         <v>0</v>
@@ -655,30 +859,30 @@
         <v>1</v>
       </c>
       <c r="I13" t="n" s="0">
-        <v>18.0679988861084</v>
+        <v>26.687999725341797</v>
       </c>
       <c r="J13" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>15.0</v>
+        <v>649.0</v>
       </c>
       <c r="E14" t="n" s="0">
-        <v>797.0</v>
+        <v>34.0</v>
       </c>
       <c r="F14" t="n" s="0">
-        <v>175.0</v>
+        <v>27.0</v>
       </c>
       <c r="G14" t="b" s="0">
         <v>0</v>
@@ -687,30 +891,30 @@
         <v>1</v>
       </c>
       <c r="I14" t="n" s="0">
-        <v>1.1130000352859497</v>
+        <v>20.98200035095215</v>
       </c>
       <c r="J14" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>15.0</v>
+        <v>669.0</v>
       </c>
       <c r="E15" t="n" s="0">
-        <v>801.0</v>
+        <v>94.0</v>
       </c>
       <c r="F15" t="n" s="0">
-        <v>178.0</v>
+        <v>1.0</v>
       </c>
       <c r="G15" t="b" s="0">
         <v>0</v>
@@ -719,30 +923,30 @@
         <v>1</v>
       </c>
       <c r="I15" t="n" s="0">
-        <v>1.4739999771118164</v>
+        <v>22.56599998474121</v>
       </c>
       <c r="J15" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>15.0</v>
+        <v>666.0</v>
       </c>
       <c r="E16" t="n" s="0">
-        <v>1061.0</v>
+        <v>66.0</v>
       </c>
       <c r="F16" t="n" s="0">
-        <v>184.0</v>
+        <v>6.0</v>
       </c>
       <c r="G16" t="b" s="0">
         <v>0</v>
@@ -751,30 +955,30 @@
         <v>1</v>
       </c>
       <c r="I16" t="n" s="0">
-        <v>1.2979999780654907</v>
+        <v>25.933000564575195</v>
       </c>
       <c r="J16" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>15.0</v>
+        <v>728.0</v>
       </c>
       <c r="E17" t="n" s="0">
-        <v>1099.0</v>
+        <v>18.0</v>
       </c>
       <c r="F17" t="n" s="0">
-        <v>178.0</v>
+        <v>17.0</v>
       </c>
       <c r="G17" t="b" s="0">
         <v>0</v>
@@ -783,30 +987,30 @@
         <v>1</v>
       </c>
       <c r="I17" t="n" s="0">
-        <v>2.25</v>
+        <v>25.176000595092773</v>
       </c>
       <c r="J17" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>15.0</v>
+        <v>649.0</v>
       </c>
       <c r="E18" t="n" s="0">
-        <v>1114.0</v>
+        <v>4.0</v>
       </c>
       <c r="F18" t="n" s="0">
-        <v>203.0</v>
+        <v>4.0</v>
       </c>
       <c r="G18" t="b" s="0">
         <v>0</v>
@@ -815,42 +1019,778 @@
         <v>1</v>
       </c>
       <c r="I18" t="n" s="0">
-        <v>1.9809999465942383</v>
+        <v>20.825000762939453</v>
       </c>
       <c r="J18" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="D19" t="n" s="0">
+        <v>649.0</v>
+      </c>
+      <c r="E19" t="n" s="0">
+        <v>33.0</v>
+      </c>
+      <c r="F19" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G19" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H19" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n" s="0">
+        <v>20.834999084472656</v>
+      </c>
+      <c r="J19" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="D20" t="n" s="0">
+        <v>687.0</v>
+      </c>
+      <c r="E20" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="F20" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G20" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n" s="0">
+        <v>21.98200035095215</v>
+      </c>
+      <c r="J20" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D21" t="n" s="0">
+        <v>675.0</v>
+      </c>
+      <c r="E21" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F21" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G21" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H21" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n" s="0">
+        <v>17.93000030517578</v>
+      </c>
+      <c r="J21" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
         <v>59</v>
       </c>
-      <c r="B19" t="s" s="0">
-        <v>60</v>
-      </c>
-      <c r="C19" t="s" s="0">
-        <v>61</v>
-      </c>
-      <c r="D19" t="n" s="0">
+      <c r="B22" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="D22" t="n" s="0">
+        <v>649.0</v>
+      </c>
+      <c r="E22" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="F22" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="G22" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H22" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n" s="0">
+        <v>24.16699981689453</v>
+      </c>
+      <c r="J22" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="D23" t="n" s="0">
+        <v>675.0</v>
+      </c>
+      <c r="E23" t="n" s="0">
         <v>15.0</v>
       </c>
-      <c r="E19" t="n" s="0">
-        <v>1069.0</v>
-      </c>
-      <c r="F19" t="n" s="0">
-        <v>184.0</v>
-      </c>
-      <c r="G19" t="b" s="0">
-        <v>0</v>
-      </c>
-      <c r="H19" t="b" s="0">
-        <v>1</v>
-      </c>
-      <c r="I19" t="n" s="0">
-        <v>2.059000015258789</v>
-      </c>
-      <c r="J19" t="b" s="0">
-        <v>1</v>
+      <c r="F23" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G23" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H23" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n" s="0">
+        <v>18.114999771118164</v>
+      </c>
+      <c r="J23" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="D24" t="n" s="0">
+        <v>649.0</v>
+      </c>
+      <c r="E24" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F24" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G24" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H24" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n" s="0">
+        <v>14.88599967956543</v>
+      </c>
+      <c r="J24" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="C25" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="D25" t="n" s="0">
+        <v>645.0</v>
+      </c>
+      <c r="E25" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="F25" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G25" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H25" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n" s="0">
+        <v>35.507999420166016</v>
+      </c>
+      <c r="J25" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="C26" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="D26" t="n" s="0">
+        <v>645.0</v>
+      </c>
+      <c r="E26" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="F26" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="G26" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H26" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n" s="0">
+        <v>17.15999984741211</v>
+      </c>
+      <c r="J26" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="C27" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="D27" t="n" s="0">
+        <v>645.0</v>
+      </c>
+      <c r="E27" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="F27" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G27" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H27" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n" s="0">
+        <v>25.888999938964844</v>
+      </c>
+      <c r="J27" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="C28" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="D28" t="n" s="0">
+        <v>644.0</v>
+      </c>
+      <c r="E28" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F28" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G28" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H28" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n" s="0">
+        <v>13.855999946594238</v>
+      </c>
+      <c r="J28" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="C29" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="D29" t="n" s="0">
+        <v>645.0</v>
+      </c>
+      <c r="E29" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F29" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G29" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H29" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n" s="0">
+        <v>18.340999603271484</v>
+      </c>
+      <c r="J29" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="C30" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="D30" t="n" s="0">
+        <v>644.0</v>
+      </c>
+      <c r="E30" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F30" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G30" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H30" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n" s="0">
+        <v>17.961999893188477</v>
+      </c>
+      <c r="J30" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="C31" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="D31" t="n" s="0">
+        <v>643.0</v>
+      </c>
+      <c r="E31" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F31" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G31" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H31" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n" s="0">
+        <v>14.942000389099121</v>
+      </c>
+      <c r="J31" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="C32" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="D32" t="n" s="0">
+        <v>645.0</v>
+      </c>
+      <c r="E32" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F32" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G32" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H32" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n" s="0">
+        <v>13.729000091552734</v>
+      </c>
+      <c r="J32" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="C33" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="D33" t="n" s="0">
+        <v>644.0</v>
+      </c>
+      <c r="E33" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="F33" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="G33" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H33" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n" s="0">
+        <v>14.336999893188477</v>
+      </c>
+      <c r="J33" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="C34" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="D34" t="n" s="0">
+        <v>644.0</v>
+      </c>
+      <c r="E34" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="F34" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="G34" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H34" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n" s="0">
+        <v>13.770000457763672</v>
+      </c>
+      <c r="J34" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="C35" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="D35" t="n" s="0">
+        <v>644.0</v>
+      </c>
+      <c r="E35" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F35" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G35" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H35" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n" s="0">
+        <v>13.467000007629395</v>
+      </c>
+      <c r="J35" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="C36" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="D36" t="n" s="0">
+        <v>645.0</v>
+      </c>
+      <c r="E36" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="F36" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="G36" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H36" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n" s="0">
+        <v>12.840999603271484</v>
+      </c>
+      <c r="J36" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="C37" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="D37" t="n" s="0">
+        <v>643.0</v>
+      </c>
+      <c r="E37" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F37" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G37" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H37" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n" s="0">
+        <v>10.697999954223633</v>
+      </c>
+      <c r="J37" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="C38" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="D38" t="n" s="0">
+        <v>643.0</v>
+      </c>
+      <c r="E38" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F38" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G38" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H38" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n" s="0">
+        <v>9.005999565124512</v>
+      </c>
+      <c r="J38" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="C39" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="D39" t="n" s="0">
+        <v>644.0</v>
+      </c>
+      <c r="E39" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F39" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G39" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H39" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n" s="0">
+        <v>11.4399995803833</v>
+      </c>
+      <c r="J39" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="C40" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="D40" t="n" s="0">
+        <v>644.0</v>
+      </c>
+      <c r="E40" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F40" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G40" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H40" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n" s="0">
+        <v>8.79699993133545</v>
+      </c>
+      <c r="J40" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="C41" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="D41" t="n" s="0">
+        <v>644.0</v>
+      </c>
+      <c r="E41" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="F41" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="G41" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H41" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I41" t="n" s="0">
+        <v>7.589000225067139</v>
+      </c>
+      <c r="J41" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="B42" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="C42" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="D42" t="n" s="0">
+        <v>639.0</v>
+      </c>
+      <c r="E42" t="n" s="0">
+        <v>48.0</v>
+      </c>
+      <c r="F42" t="n" s="0">
+        <v>44.0</v>
+      </c>
+      <c r="G42" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H42" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I42" t="n" s="0">
+        <v>6.197000026702881</v>
+      </c>
+      <c r="J42" t="b" s="0">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
